--- a/reports/latest/Test Results/Excel/Automation_Test_Report.xlsx
+++ b/reports/latest/Test Results/Excel/Automation_Test_Report.xlsx
@@ -31747,14 +31747,14 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Navigation</t>
+          <t>Profile Management</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>0</v>
@@ -31768,14 +31768,14 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>File Upload</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>1</v>
@@ -31789,35 +31789,35 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Search &amp; Filters</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>100.0 %</t>
+          <t>95.0 %</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Registration</t>
+          <t>Regression Suite</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>0</v>
@@ -31831,35 +31831,35 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
         <v>20</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>95.0 %</t>
+          <t>100.0 %</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Offline Handling</t>
+          <t>Registration</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>0</v>
@@ -31873,35 +31873,35 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Error Handling</t>
+          <t>Forms &amp; Inputs</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>100.0 %</t>
+          <t>98.8 %</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Session Management</t>
+          <t>CRUD Operations</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>0</v>
@@ -31915,35 +31915,35 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Forms &amp; Inputs</t>
+          <t>Search &amp; Filters</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>98.8 %</t>
+          <t>100.0 %</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Regression Suite</t>
+          <t>Offline Handling</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>0</v>
@@ -31957,28 +31957,28 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>CRUD Operations</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>100.0 %</t>
+          <t>95.0 %</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Error Handling</t>
         </is>
       </c>
       <c r="B14" s="6" t="n">
@@ -31999,35 +31999,35 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Session Management</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>95.0 %</t>
+          <t>100.0 %</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Profile Management</t>
+          <t>Navigation</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D16" s="6" t="n">
         <v>0</v>
